--- a/BWI/bestwine_output/bestwine_Kyrgyzstan.xlsx
+++ b/BWI/bestwine_output/bestwine_Kyrgyzstan.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1083,6 +1083,91 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>NOVA-VINA, OSOO</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>167903</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Kyrgyzstan</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Bishkek</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>110 ul. Bokonbaeva</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.srws.net</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2288505</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>info@srws.net</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>+996 312 300 573</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>107625-3301-OOO</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr"/>
+      <c r="V6" s="2" t="inlineStr"/>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>Lyuka Mae Shenaf</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
